--- a/results/screening/title_abstract_screening_completed.xlsx
+++ b/results/screening/title_abstract_screening_completed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Projects\srma-agent-toolkit\results\screening\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1769F3-AE27-4A3E-B1C1-F2D2B9E2C217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4962E3FD-71C9-429F-9522-ECD5C4EB8485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28740" yWindow="-60" windowWidth="28920" windowHeight="15600" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3600" yWindow="-1080" windowWidth="28965" windowHeight="15825" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -34,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5508" uniqueCount="1542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5510" uniqueCount="1543">
   <si>
     <t>decisions</t>
   </si>
@@ -5050,6 +5047,10 @@
   </si>
   <si>
     <t>TAVR</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BACKGROUND: In the CANVAS (Canagliflozin Cardiovascular Assessment Study) program, canagliflozin reduced the risk of heart failure (HF) hospitalization among individuals with type 2 diabetes mellitus (T2DM). OBJECTIVES: The purpose of this study was to evaluate heterogeneity in absolute and relative treatment effects of canagliflozin on HF hospitalization according to baseline HF risk as assessed by diabetes-specific HF risk scores (WATCH-DM [Weight (body mass index), Age, hyperTension, Creatinine, HDL-C, Diabetes control (fasting plasma glucose) and QRS Duration, MI and CABG] and TRS-HFDM [TIMI Risk Score for HF in Diabetes]). METHODS: Participants in the CANVAS trial were categorized into low, medium, and high risk for HF using the WATCH-DM score (for participants without prevalent HF) and the TRS-HFDM score (for all participants). The outcome of interest was time to first HF hospitalization. The treatment effect of canagliflozin vs placebo for HF hospitalization was compared across risk strata. RESULTS: Among 10,137 participants with available HF data, 1,446 (14.3%) had HF at baseline. Among participants without baseline HF, WATCH-DM risk category did not modify the treatment effect of canagliflozin (vs placebo) on HF hospitalization (P interaction = 0.56). However, the absolute and relative risk reduction with canagliflozin was numerically greater in the high-risk group (cumulative incidence, canagliflozin vs placebo: 8.1% vs 12.7%; HR: 0.62 [95% CI: 0.37-0.93]; P = 0.03; number needed to treat: 22) than in the low- and intermediate-risk groups. When overall study participants were categorized according to the TRS-HFDM score, a statistically significant difference in the treatment effect of canagliflozin across risk strata was observed (P interaction = 0.04). Canagliflozin significantly reduced the risk of HF hospitalization by 39% in the high-risk group (HR: 0.61 [95% CI: 0.48-0.78]; P &lt; 0.001; number needed to treat: 20) but not in the intermediate- or low-risk groups. CONCLUSIONS: Among participants with T2DM, the WATCH-DM and TRS-HFDM can reliably identify those at high risk for HF hospitalization and most likely to benefit from canagliflozin.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -5175,39 +5176,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <b/>
@@ -5573,19 +5542,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.73046875" customWidth="1"/>
+    <col min="2" max="2" width="100.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -5593,7 +5562,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -5601,7 +5570,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -5609,7 +5578,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
@@ -5617,7 +5586,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
@@ -5625,7 +5594,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -5633,7 +5602,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
@@ -5641,7 +5610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
@@ -5649,7 +5618,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
@@ -5657,7 +5626,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -5665,7 +5634,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>43</v>
       </c>
@@ -5673,7 +5642,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>45</v>
       </c>
@@ -5681,7 +5650,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -5702,19 +5671,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S190"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" customWidth="1"/>
-    <col min="7" max="13" width="16.7109375" customWidth="1"/>
-    <col min="14" max="19" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" customWidth="1"/>
+    <col min="3" max="3" width="65.73046875" customWidth="1"/>
+    <col min="4" max="4" width="100.73046875" customWidth="1"/>
+    <col min="5" max="5" width="22.73046875" customWidth="1"/>
+    <col min="6" max="6" width="32.73046875" customWidth="1"/>
+    <col min="7" max="13" width="16.73046875" customWidth="1"/>
+    <col min="14" max="19" width="22.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>49</v>
       </c>
@@ -5737,7 +5706,7 @@
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>50</v>
       </c>
@@ -5760,7 +5729,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="5"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
@@ -5819,7 +5788,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>68</v>
       </c>
@@ -5868,7 +5837,7 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>81</v>
       </c>
@@ -5917,7 +5886,7 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>93</v>
       </c>
@@ -5968,7 +5937,7 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>104</v>
       </c>
@@ -6017,7 +5986,7 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>114</v>
       </c>
@@ -6066,7 +6035,7 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>123</v>
       </c>
@@ -6117,7 +6086,7 @@
       </c>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>132</v>
       </c>
@@ -6166,7 +6135,7 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>139</v>
       </c>
@@ -6176,10 +6145,12 @@
       <c r="C12" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" s="2"/>
+      <c r="D12" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>142</v>
       </c>
@@ -6208,12 +6179,14 @@
         <v>80</v>
       </c>
       <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
+      <c r="P12" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>148</v>
       </c>
@@ -6260,7 +6233,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>157</v>
       </c>
@@ -6307,7 +6280,7 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>166</v>
       </c>
@@ -6354,7 +6327,7 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>175</v>
       </c>
@@ -6401,7 +6374,7 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>185</v>
       </c>
@@ -6448,7 +6421,7 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>194</v>
       </c>
@@ -6495,7 +6468,7 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
     </row>
-    <row r="19" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>204</v>
       </c>
@@ -6542,7 +6515,7 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
     </row>
-    <row r="20" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>212</v>
       </c>
@@ -6589,7 +6562,7 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
     </row>
-    <row r="21" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>220</v>
       </c>
@@ -6636,7 +6609,7 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>228</v>
       </c>
@@ -6683,7 +6656,7 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>237</v>
       </c>
@@ -6730,7 +6703,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>245</v>
       </c>
@@ -6777,7 +6750,7 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>254</v>
       </c>
@@ -6824,7 +6797,7 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>261</v>
       </c>
@@ -6871,7 +6844,7 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
     </row>
-    <row r="27" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>268</v>
       </c>
@@ -6918,7 +6891,7 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
     </row>
-    <row r="28" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>277</v>
       </c>
@@ -6961,7 +6934,7 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
     </row>
-    <row r="29" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>285</v>
       </c>
@@ -7004,7 +6977,7 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
     </row>
-    <row r="30" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>292</v>
       </c>
@@ -7047,7 +7020,7 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
     </row>
-    <row r="31" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>300</v>
       </c>
@@ -7090,7 +7063,7 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
     </row>
-    <row r="32" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>309</v>
       </c>
@@ -7133,7 +7106,7 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
     </row>
-    <row r="33" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>317</v>
       </c>
@@ -7176,7 +7149,7 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
     </row>
-    <row r="34" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>324</v>
       </c>
@@ -7219,7 +7192,7 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
     </row>
-    <row r="35" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>331</v>
       </c>
@@ -7262,7 +7235,7 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
     </row>
-    <row r="36" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>338</v>
       </c>
@@ -7305,7 +7278,7 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
     </row>
-    <row r="37" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>345</v>
       </c>
@@ -7348,7 +7321,7 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>352</v>
       </c>
@@ -7391,7 +7364,7 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
     </row>
-    <row r="39" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>359</v>
       </c>
@@ -7434,7 +7407,7 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
     </row>
-    <row r="40" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>367</v>
       </c>
@@ -7477,7 +7450,7 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
     </row>
-    <row r="41" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
         <v>374</v>
       </c>
@@ -7520,7 +7493,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
     </row>
-    <row r="42" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>381</v>
       </c>
@@ -7563,7 +7536,7 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
     </row>
-    <row r="43" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>388</v>
       </c>
@@ -7606,7 +7579,7 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
     </row>
-    <row r="44" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>395</v>
       </c>
@@ -7649,7 +7622,7 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
     </row>
-    <row r="45" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>402</v>
       </c>
@@ -7692,7 +7665,7 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
     </row>
-    <row r="46" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
         <v>410</v>
       </c>
@@ -7735,7 +7708,7 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
     </row>
-    <row r="47" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>417</v>
       </c>
@@ -7778,7 +7751,7 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
     </row>
-    <row r="48" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>424</v>
       </c>
@@ -7821,7 +7794,7 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
     </row>
-    <row r="49" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>431</v>
       </c>
@@ -7864,7 +7837,7 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
     </row>
-    <row r="50" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>438</v>
       </c>
@@ -7907,7 +7880,7 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
     </row>
-    <row r="51" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>445</v>
       </c>
@@ -7950,7 +7923,7 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
     </row>
-    <row r="52" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>452</v>
       </c>
@@ -7993,7 +7966,7 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
     </row>
-    <row r="53" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>459</v>
       </c>
@@ -8036,7 +8009,7 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
     </row>
-    <row r="54" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>466</v>
       </c>
@@ -8079,7 +8052,7 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
     </row>
-    <row r="55" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>473</v>
       </c>
@@ -8122,7 +8095,7 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
     </row>
-    <row r="56" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
         <v>480</v>
       </c>
@@ -8165,7 +8138,7 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
     </row>
-    <row r="57" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>487</v>
       </c>
@@ -8208,7 +8181,7 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
     </row>
-    <row r="58" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>494</v>
       </c>
@@ -8251,7 +8224,7 @@
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
     </row>
-    <row r="59" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>501</v>
       </c>
@@ -8294,7 +8267,7 @@
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
     </row>
-    <row r="60" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
         <v>508</v>
       </c>
@@ -8339,7 +8312,7 @@
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
     </row>
-    <row r="61" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
         <v>518</v>
       </c>
@@ -8384,7 +8357,7 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
     </row>
-    <row r="62" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
         <v>525</v>
       </c>
@@ -8429,7 +8402,7 @@
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
     </row>
-    <row r="63" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>532</v>
       </c>
@@ -8474,7 +8447,7 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
     </row>
-    <row r="64" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>539</v>
       </c>
@@ -8519,7 +8492,7 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
     </row>
-    <row r="65" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>546</v>
       </c>
@@ -8564,7 +8537,7 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
     </row>
-    <row r="66" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>552</v>
       </c>
@@ -8609,7 +8582,7 @@
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
     </row>
-    <row r="67" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>559</v>
       </c>
@@ -8654,7 +8627,7 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>566</v>
       </c>
@@ -8699,7 +8672,7 @@
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
     </row>
-    <row r="69" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>573</v>
       </c>
@@ -8742,7 +8715,7 @@
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
     </row>
-    <row r="70" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>579</v>
       </c>
@@ -8785,7 +8758,7 @@
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
     </row>
-    <row r="71" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>584</v>
       </c>
@@ -8830,7 +8803,7 @@
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
     </row>
-    <row r="72" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>591</v>
       </c>
@@ -8875,7 +8848,7 @@
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
     </row>
-    <row r="73" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
         <v>598</v>
       </c>
@@ -8920,7 +8893,7 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
     </row>
-    <row r="74" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
         <v>604</v>
       </c>
@@ -8965,7 +8938,7 @@
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
     </row>
-    <row r="75" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>610</v>
       </c>
@@ -9010,7 +8983,7 @@
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
     </row>
-    <row r="76" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
         <v>617</v>
       </c>
@@ -9055,7 +9028,7 @@
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
     </row>
-    <row r="77" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>624</v>
       </c>
@@ -9100,7 +9073,7 @@
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
     </row>
-    <row r="78" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
         <v>631</v>
       </c>
@@ -9145,7 +9118,7 @@
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
     </row>
-    <row r="79" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>638</v>
       </c>
@@ -9190,7 +9163,7 @@
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
     </row>
-    <row r="80" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
         <v>645</v>
       </c>
@@ -9235,7 +9208,7 @@
       <c r="R80" s="2"/>
       <c r="S80" s="2"/>
     </row>
-    <row r="81" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>652</v>
       </c>
@@ -9280,7 +9253,7 @@
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
     </row>
-    <row r="82" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
         <v>659</v>
       </c>
@@ -9325,7 +9298,7 @@
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
     </row>
-    <row r="83" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
         <v>666</v>
       </c>
@@ -9372,7 +9345,7 @@
       <c r="R83" s="2"/>
       <c r="S83" s="2"/>
     </row>
-    <row r="84" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>676</v>
       </c>
@@ -9419,7 +9392,7 @@
       <c r="R84" s="2"/>
       <c r="S84" s="2"/>
     </row>
-    <row r="85" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>685</v>
       </c>
@@ -9466,7 +9439,7 @@
       <c r="R85" s="2"/>
       <c r="S85" s="2"/>
     </row>
-    <row r="86" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
         <v>693</v>
       </c>
@@ -9513,7 +9486,7 @@
       <c r="R86" s="2"/>
       <c r="S86" s="2"/>
     </row>
-    <row r="87" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>701</v>
       </c>
@@ -9560,7 +9533,7 @@
       <c r="R87" s="2"/>
       <c r="S87" s="2"/>
     </row>
-    <row r="88" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
         <v>710</v>
       </c>
@@ -9607,7 +9580,7 @@
       <c r="R88" s="2"/>
       <c r="S88" s="2"/>
     </row>
-    <row r="89" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
         <v>719</v>
       </c>
@@ -9654,7 +9627,7 @@
       <c r="R89" s="2"/>
       <c r="S89" s="2"/>
     </row>
-    <row r="90" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
         <v>727</v>
       </c>
@@ -9699,7 +9672,7 @@
       <c r="R90" s="2"/>
       <c r="S90" s="2"/>
     </row>
-    <row r="91" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
         <v>734</v>
       </c>
@@ -9746,7 +9719,7 @@
       <c r="R91" s="2"/>
       <c r="S91" s="2"/>
     </row>
-    <row r="92" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>742</v>
       </c>
@@ -9793,7 +9766,7 @@
       <c r="R92" s="2"/>
       <c r="S92" s="2"/>
     </row>
-    <row r="93" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
         <v>751</v>
       </c>
@@ -9840,7 +9813,7 @@
       <c r="R93" s="2"/>
       <c r="S93" s="2"/>
     </row>
-    <row r="94" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
         <v>758</v>
       </c>
@@ -9887,7 +9860,7 @@
       <c r="R94" s="2"/>
       <c r="S94" s="2"/>
     </row>
-    <row r="95" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
         <v>766</v>
       </c>
@@ -9934,7 +9907,7 @@
       <c r="R95" s="2"/>
       <c r="S95" s="2"/>
     </row>
-    <row r="96" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>775</v>
       </c>
@@ -9981,7 +9954,7 @@
       <c r="R96" s="2"/>
       <c r="S96" s="2"/>
     </row>
-    <row r="97" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
         <v>783</v>
       </c>
@@ -10028,7 +10001,7 @@
       <c r="R97" s="2"/>
       <c r="S97" s="2"/>
     </row>
-    <row r="98" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
         <v>792</v>
       </c>
@@ -10075,7 +10048,7 @@
       <c r="R98" s="2"/>
       <c r="S98" s="2"/>
     </row>
-    <row r="99" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
         <v>801</v>
       </c>
@@ -10122,7 +10095,7 @@
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
     </row>
-    <row r="100" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
         <v>808</v>
       </c>
@@ -10169,7 +10142,7 @@
       <c r="R100" s="2"/>
       <c r="S100" s="2"/>
     </row>
-    <row r="101" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
         <v>816</v>
       </c>
@@ -10216,7 +10189,7 @@
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
     </row>
-    <row r="102" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
         <v>824</v>
       </c>
@@ -10263,7 +10236,7 @@
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
     </row>
-    <row r="103" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
         <v>832</v>
       </c>
@@ -10310,7 +10283,7 @@
       <c r="R103" s="2"/>
       <c r="S103" s="2"/>
     </row>
-    <row r="104" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
         <v>839</v>
       </c>
@@ -10357,7 +10330,7 @@
       <c r="R104" s="2"/>
       <c r="S104" s="2"/>
     </row>
-    <row r="105" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
         <v>848</v>
       </c>
@@ -10404,7 +10377,7 @@
       <c r="R105" s="2"/>
       <c r="S105" s="2"/>
     </row>
-    <row r="106" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
         <v>856</v>
       </c>
@@ -10451,7 +10424,7 @@
       <c r="R106" s="2"/>
       <c r="S106" s="2"/>
     </row>
-    <row r="107" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
         <v>863</v>
       </c>
@@ -10498,7 +10471,7 @@
       <c r="R107" s="2"/>
       <c r="S107" s="2"/>
     </row>
-    <row r="108" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
         <v>871</v>
       </c>
@@ -10545,7 +10518,7 @@
       <c r="R108" s="2"/>
       <c r="S108" s="2"/>
     </row>
-    <row r="109" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
         <v>880</v>
       </c>
@@ -10592,7 +10565,7 @@
       <c r="R109" s="2"/>
       <c r="S109" s="2"/>
     </row>
-    <row r="110" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
         <v>889</v>
       </c>
@@ -10639,7 +10612,7 @@
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
     </row>
-    <row r="111" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
         <v>897</v>
       </c>
@@ -10686,7 +10659,7 @@
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
     </row>
-    <row r="112" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
         <v>904</v>
       </c>
@@ -10733,7 +10706,7 @@
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
     </row>
-    <row r="113" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
         <v>912</v>
       </c>
@@ -10780,7 +10753,7 @@
       <c r="R113" s="2"/>
       <c r="S113" s="2"/>
     </row>
-    <row r="114" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
         <v>920</v>
       </c>
@@ -10827,7 +10800,7 @@
       <c r="R114" s="2"/>
       <c r="S114" s="2"/>
     </row>
-    <row r="115" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
         <v>928</v>
       </c>
@@ -10874,7 +10847,7 @@
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
     </row>
-    <row r="116" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
         <v>936</v>
       </c>
@@ -10921,7 +10894,7 @@
       <c r="R116" s="2"/>
       <c r="S116" s="2"/>
     </row>
-    <row r="117" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
         <v>944</v>
       </c>
@@ -10968,7 +10941,7 @@
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
     </row>
-    <row r="118" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
         <v>951</v>
       </c>
@@ -11015,7 +10988,7 @@
       <c r="R118" s="2"/>
       <c r="S118" s="2"/>
     </row>
-    <row r="119" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="2" t="s">
         <v>959</v>
       </c>
@@ -11062,7 +11035,7 @@
       <c r="R119" s="2"/>
       <c r="S119" s="2"/>
     </row>
-    <row r="120" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="2" t="s">
         <v>966</v>
       </c>
@@ -11109,7 +11082,7 @@
       <c r="R120" s="2"/>
       <c r="S120" s="2"/>
     </row>
-    <row r="121" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="2" t="s">
         <v>974</v>
       </c>
@@ -11156,7 +11129,7 @@
       <c r="R121" s="2"/>
       <c r="S121" s="2"/>
     </row>
-    <row r="122" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
         <v>982</v>
       </c>
@@ -11203,7 +11176,7 @@
       <c r="R122" s="2"/>
       <c r="S122" s="2"/>
     </row>
-    <row r="123" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="2" t="s">
         <v>990</v>
       </c>
@@ -11250,7 +11223,7 @@
       <c r="R123" s="2"/>
       <c r="S123" s="2"/>
     </row>
-    <row r="124" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
         <v>999</v>
       </c>
@@ -11297,7 +11270,7 @@
       <c r="R124" s="2"/>
       <c r="S124" s="2"/>
     </row>
-    <row r="125" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="2" t="s">
         <v>1007</v>
       </c>
@@ -11344,7 +11317,7 @@
       <c r="R125" s="2"/>
       <c r="S125" s="2"/>
     </row>
-    <row r="126" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="2" t="s">
         <v>1014</v>
       </c>
@@ -11391,7 +11364,7 @@
       <c r="R126" s="2"/>
       <c r="S126" s="2"/>
     </row>
-    <row r="127" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
         <v>1022</v>
       </c>
@@ -11438,7 +11411,7 @@
       <c r="R127" s="2"/>
       <c r="S127" s="2"/>
     </row>
-    <row r="128" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
         <v>1030</v>
       </c>
@@ -11485,7 +11458,7 @@
       <c r="R128" s="2"/>
       <c r="S128" s="2"/>
     </row>
-    <row r="129" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
         <v>1038</v>
       </c>
@@ -11532,7 +11505,7 @@
       <c r="R129" s="2"/>
       <c r="S129" s="2"/>
     </row>
-    <row r="130" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="2" t="s">
         <v>1046</v>
       </c>
@@ -11579,7 +11552,7 @@
       <c r="R130" s="2"/>
       <c r="S130" s="2"/>
     </row>
-    <row r="131" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="2" t="s">
         <v>1054</v>
       </c>
@@ -11626,7 +11599,7 @@
       <c r="R131" s="2"/>
       <c r="S131" s="2"/>
     </row>
-    <row r="132" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="2" t="s">
         <v>1062</v>
       </c>
@@ -11673,7 +11646,7 @@
       <c r="R132" s="2"/>
       <c r="S132" s="2"/>
     </row>
-    <row r="133" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A133" s="2" t="s">
         <v>1072</v>
       </c>
@@ -11720,7 +11693,7 @@
       <c r="R133" s="2"/>
       <c r="S133" s="2"/>
     </row>
-    <row r="134" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="2" t="s">
         <v>1080</v>
       </c>
@@ -11767,7 +11740,7 @@
       <c r="R134" s="2"/>
       <c r="S134" s="2"/>
     </row>
-    <row r="135" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="2" t="s">
         <v>1087</v>
       </c>
@@ -11814,7 +11787,7 @@
       <c r="R135" s="2"/>
       <c r="S135" s="2"/>
     </row>
-    <row r="136" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A136" s="2" t="s">
         <v>1095</v>
       </c>
@@ -11861,7 +11834,7 @@
       <c r="R136" s="2"/>
       <c r="S136" s="2"/>
     </row>
-    <row r="137" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
         <v>1103</v>
       </c>
@@ -11906,7 +11879,7 @@
       <c r="R137" s="2"/>
       <c r="S137" s="2"/>
     </row>
-    <row r="138" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
         <v>1111</v>
       </c>
@@ -11951,7 +11924,7 @@
       <c r="R138" s="2"/>
       <c r="S138" s="2"/>
     </row>
-    <row r="139" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="2" t="s">
         <v>1118</v>
       </c>
@@ -11998,7 +11971,7 @@
       <c r="R139" s="2"/>
       <c r="S139" s="2"/>
     </row>
-    <row r="140" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
         <v>1126</v>
       </c>
@@ -12045,7 +12018,7 @@
       <c r="R140" s="2"/>
       <c r="S140" s="2"/>
     </row>
-    <row r="141" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
         <v>1134</v>
       </c>
@@ -12092,7 +12065,7 @@
       <c r="R141" s="2"/>
       <c r="S141" s="2"/>
     </row>
-    <row r="142" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A142" s="2" t="s">
         <v>1141</v>
       </c>
@@ -12139,7 +12112,7 @@
       <c r="R142" s="2"/>
       <c r="S142" s="2"/>
     </row>
-    <row r="143" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="2" t="s">
         <v>1150</v>
       </c>
@@ -12186,7 +12159,7 @@
       <c r="R143" s="2"/>
       <c r="S143" s="2"/>
     </row>
-    <row r="144" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A144" s="2" t="s">
         <v>1158</v>
       </c>
@@ -12233,7 +12206,7 @@
       <c r="R144" s="2"/>
       <c r="S144" s="2"/>
     </row>
-    <row r="145" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A145" s="2" t="s">
         <v>1166</v>
       </c>
@@ -12278,7 +12251,7 @@
       <c r="R145" s="2"/>
       <c r="S145" s="2"/>
     </row>
-    <row r="146" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A146" s="2" t="s">
         <v>1174</v>
       </c>
@@ -12325,7 +12298,7 @@
       <c r="R146" s="2"/>
       <c r="S146" s="2"/>
     </row>
-    <row r="147" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
         <v>1182</v>
       </c>
@@ -12372,7 +12345,7 @@
       <c r="R147" s="2"/>
       <c r="S147" s="2"/>
     </row>
-    <row r="148" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
         <v>1190</v>
       </c>
@@ -12419,7 +12392,7 @@
       <c r="R148" s="2"/>
       <c r="S148" s="2"/>
     </row>
-    <row r="149" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
         <v>1197</v>
       </c>
@@ -12466,7 +12439,7 @@
       <c r="R149" s="2"/>
       <c r="S149" s="2"/>
     </row>
-    <row r="150" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
         <v>1205</v>
       </c>
@@ -12513,7 +12486,7 @@
       <c r="R150" s="2"/>
       <c r="S150" s="2"/>
     </row>
-    <row r="151" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
         <v>1212</v>
       </c>
@@ -12560,7 +12533,7 @@
       <c r="R151" s="2"/>
       <c r="S151" s="2"/>
     </row>
-    <row r="152" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
         <v>1219</v>
       </c>
@@ -12607,7 +12580,7 @@
       <c r="R152" s="2"/>
       <c r="S152" s="2"/>
     </row>
-    <row r="153" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="2" t="s">
         <v>1228</v>
       </c>
@@ -12654,7 +12627,7 @@
       <c r="R153" s="2"/>
       <c r="S153" s="2"/>
     </row>
-    <row r="154" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A154" s="2" t="s">
         <v>1235</v>
       </c>
@@ -12701,7 +12674,7 @@
       <c r="R154" s="2"/>
       <c r="S154" s="2"/>
     </row>
-    <row r="155" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A155" s="2" t="s">
         <v>1243</v>
       </c>
@@ -12748,7 +12721,7 @@
       <c r="R155" s="2"/>
       <c r="S155" s="2"/>
     </row>
-    <row r="156" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A156" s="2" t="s">
         <v>1251</v>
       </c>
@@ -12795,7 +12768,7 @@
       <c r="R156" s="2"/>
       <c r="S156" s="2"/>
     </row>
-    <row r="157" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A157" s="2" t="s">
         <v>1258</v>
       </c>
@@ -12842,7 +12815,7 @@
       <c r="R157" s="2"/>
       <c r="S157" s="2"/>
     </row>
-    <row r="158" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A158" s="2" t="s">
         <v>1266</v>
       </c>
@@ -12889,7 +12862,7 @@
       <c r="R158" s="2"/>
       <c r="S158" s="2"/>
     </row>
-    <row r="159" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A159" s="2" t="s">
         <v>1274</v>
       </c>
@@ -12936,7 +12909,7 @@
       <c r="R159" s="2"/>
       <c r="S159" s="2"/>
     </row>
-    <row r="160" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A160" s="2" t="s">
         <v>1281</v>
       </c>
@@ -12981,7 +12954,7 @@
       <c r="R160" s="2"/>
       <c r="S160" s="2"/>
     </row>
-    <row r="161" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A161" s="2" t="s">
         <v>1288</v>
       </c>
@@ -13028,7 +13001,7 @@
       <c r="R161" s="2"/>
       <c r="S161" s="2"/>
     </row>
-    <row r="162" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A162" s="2" t="s">
         <v>1296</v>
       </c>
@@ -13075,7 +13048,7 @@
       <c r="R162" s="2"/>
       <c r="S162" s="2"/>
     </row>
-    <row r="163" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A163" s="2" t="s">
         <v>1304</v>
       </c>
@@ -13122,7 +13095,7 @@
       <c r="R163" s="2"/>
       <c r="S163" s="2"/>
     </row>
-    <row r="164" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A164" s="2" t="s">
         <v>1313</v>
       </c>
@@ -13169,7 +13142,7 @@
       <c r="R164" s="2"/>
       <c r="S164" s="2"/>
     </row>
-    <row r="165" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A165" s="2" t="s">
         <v>1321</v>
       </c>
@@ -13216,7 +13189,7 @@
       <c r="R165" s="2"/>
       <c r="S165" s="2"/>
     </row>
-    <row r="166" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A166" s="2" t="s">
         <v>1329</v>
       </c>
@@ -13261,7 +13234,7 @@
       <c r="R166" s="2"/>
       <c r="S166" s="2"/>
     </row>
-    <row r="167" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A167" s="2" t="s">
         <v>1335</v>
       </c>
@@ -13308,7 +13281,7 @@
       <c r="R167" s="2"/>
       <c r="S167" s="2"/>
     </row>
-    <row r="168" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A168" s="2" t="s">
         <v>1342</v>
       </c>
@@ -13355,7 +13328,7 @@
       <c r="R168" s="2"/>
       <c r="S168" s="2"/>
     </row>
-    <row r="169" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A169" s="2" t="s">
         <v>1349</v>
       </c>
@@ -13402,7 +13375,7 @@
       <c r="R169" s="2"/>
       <c r="S169" s="2"/>
     </row>
-    <row r="170" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A170" s="2" t="s">
         <v>1356</v>
       </c>
@@ -13449,7 +13422,7 @@
       <c r="R170" s="2"/>
       <c r="S170" s="2"/>
     </row>
-    <row r="171" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="2" t="s">
         <v>1364</v>
       </c>
@@ -13494,7 +13467,7 @@
       <c r="R171" s="2"/>
       <c r="S171" s="2"/>
     </row>
-    <row r="172" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="2" t="s">
         <v>1371</v>
       </c>
@@ -13541,7 +13514,7 @@
       <c r="R172" s="2"/>
       <c r="S172" s="2"/>
     </row>
-    <row r="173" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="2" t="s">
         <v>1379</v>
       </c>
@@ -13588,7 +13561,7 @@
       <c r="R173" s="2"/>
       <c r="S173" s="2"/>
     </row>
-    <row r="174" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="2" t="s">
         <v>1387</v>
       </c>
@@ -13635,7 +13608,7 @@
       <c r="R174" s="2"/>
       <c r="S174" s="2"/>
     </row>
-    <row r="175" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="2" t="s">
         <v>1395</v>
       </c>
@@ -13680,7 +13653,7 @@
       <c r="R175" s="2"/>
       <c r="S175" s="2"/>
     </row>
-    <row r="176" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="2" t="s">
         <v>1401</v>
       </c>
@@ -13725,7 +13698,7 @@
       <c r="R176" s="2"/>
       <c r="S176" s="2"/>
     </row>
-    <row r="177" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="2" t="s">
         <v>1409</v>
       </c>
@@ -13770,7 +13743,7 @@
       <c r="R177" s="2"/>
       <c r="S177" s="2"/>
     </row>
-    <row r="178" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="2" t="s">
         <v>1415</v>
       </c>
@@ -13817,7 +13790,7 @@
       <c r="R178" s="2"/>
       <c r="S178" s="2"/>
     </row>
-    <row r="179" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="2" t="s">
         <v>1423</v>
       </c>
@@ -13864,7 +13837,7 @@
       <c r="R179" s="2"/>
       <c r="S179" s="2"/>
     </row>
-    <row r="180" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="2" t="s">
         <v>1431</v>
       </c>
@@ -13911,7 +13884,7 @@
       <c r="R180" s="2"/>
       <c r="S180" s="2"/>
     </row>
-    <row r="181" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="2" t="s">
         <v>1439</v>
       </c>
@@ -13958,7 +13931,7 @@
       <c r="R181" s="2"/>
       <c r="S181" s="2"/>
     </row>
-    <row r="182" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="2" t="s">
         <v>1448</v>
       </c>
@@ -14003,7 +13976,7 @@
       <c r="R182" s="2"/>
       <c r="S182" s="2"/>
     </row>
-    <row r="183" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="2" t="s">
         <v>1455</v>
       </c>
@@ -14050,7 +14023,7 @@
       <c r="R183" s="2"/>
       <c r="S183" s="2"/>
     </row>
-    <row r="184" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="2" t="s">
         <v>1462</v>
       </c>
@@ -14097,7 +14070,7 @@
       <c r="R184" s="2"/>
       <c r="S184" s="2"/>
     </row>
-    <row r="185" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="2" t="s">
         <v>1470</v>
       </c>
@@ -14144,7 +14117,7 @@
       <c r="R185" s="2"/>
       <c r="S185" s="2"/>
     </row>
-    <row r="186" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="2" t="s">
         <v>1479</v>
       </c>
@@ -14191,7 +14164,7 @@
       <c r="R186" s="2"/>
       <c r="S186" s="2"/>
     </row>
-    <row r="187" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A187" s="2" t="s">
         <v>1487</v>
       </c>
@@ -14238,7 +14211,7 @@
       <c r="R187" s="2"/>
       <c r="S187" s="2"/>
     </row>
-    <row r="188" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A188" s="2" t="s">
         <v>1495</v>
       </c>
@@ -14285,7 +14258,7 @@
       <c r="R188" s="2"/>
       <c r="S188" s="2"/>
     </row>
-    <row r="189" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A189" s="2" t="s">
         <v>1502</v>
       </c>
@@ -14332,7 +14305,7 @@
       <c r="R189" s="2"/>
       <c r="S189" s="2"/>
     </row>
-    <row r="190" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A190" s="2" t="s">
         <v>1511</v>
       </c>
@@ -14384,41 +14357,25 @@
     <mergeCell ref="A2:S2"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="O5:O7 O11:O190">
-    <cfRule type="expression" dxfId="12" priority="8">
+  <conditionalFormatting sqref="E5:E190">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$O5="Exclude"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>$O5="Include"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O190">
+    <cfRule type="expression" dxfId="6" priority="5">
+      <formula>$O5="Exclude"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$O5="Include"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P190">
-    <cfRule type="expression" dxfId="10" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>AND($O5="Exclude",$P5="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O10">
-    <cfRule type="expression" dxfId="9" priority="5">
-      <formula>$O8="Exclude"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="6">
-      <formula>$O8="Include"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E7 E11:E190">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>$O5="Exclude"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>$O5="Include"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E10">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$O8="Exclude"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$O8="Include"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14453,18 +14410,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R190"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="5" width="32.7109375" customWidth="1"/>
-    <col min="6" max="12" width="16.7109375" customWidth="1"/>
-    <col min="13" max="18" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" customWidth="1"/>
+    <col min="3" max="3" width="65.73046875" customWidth="1"/>
+    <col min="4" max="4" width="100.73046875" customWidth="1"/>
+    <col min="5" max="5" width="32.73046875" customWidth="1"/>
+    <col min="6" max="12" width="16.73046875" customWidth="1"/>
+    <col min="13" max="18" width="22.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>1517</v>
       </c>
@@ -14486,7 +14443,7 @@
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>50</v>
       </c>
@@ -14508,7 +14465,7 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
@@ -14564,7 +14521,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>68</v>
       </c>
@@ -14612,7 +14569,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>81</v>
       </c>
@@ -14660,7 +14617,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>93</v>
       </c>
@@ -14708,7 +14665,7 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>104</v>
       </c>
@@ -14754,7 +14711,7 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>114</v>
       </c>
@@ -14800,7 +14757,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>123</v>
       </c>
@@ -14846,7 +14803,7 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>132</v>
       </c>
@@ -14892,7 +14849,7 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>139</v>
       </c>
@@ -14938,7 +14895,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>148</v>
       </c>
@@ -14984,7 +14941,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>157</v>
       </c>
@@ -15030,7 +14987,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>166</v>
       </c>
@@ -15076,7 +15033,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>175</v>
       </c>
@@ -15122,7 +15079,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>185</v>
       </c>
@@ -15168,7 +15125,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>194</v>
       </c>
@@ -15214,7 +15171,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>204</v>
       </c>
@@ -15260,7 +15217,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>212</v>
       </c>
@@ -15306,7 +15263,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>220</v>
       </c>
@@ -15352,7 +15309,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>228</v>
       </c>
@@ -15398,7 +15355,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>237</v>
       </c>
@@ -15444,7 +15401,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>245</v>
       </c>
@@ -15490,7 +15447,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>254</v>
       </c>
@@ -15536,7 +15493,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>261</v>
       </c>
@@ -15582,7 +15539,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>268</v>
       </c>
@@ -15628,7 +15585,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>277</v>
       </c>
@@ -15670,7 +15627,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>285</v>
       </c>
@@ -15712,7 +15669,7 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>292</v>
       </c>
@@ -15754,7 +15711,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>300</v>
       </c>
@@ -15796,7 +15753,7 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>309</v>
       </c>
@@ -15838,7 +15795,7 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>317</v>
       </c>
@@ -15880,7 +15837,7 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>324</v>
       </c>
@@ -15922,7 +15879,7 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>331</v>
       </c>
@@ -15964,7 +15921,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>338</v>
       </c>
@@ -16006,7 +15963,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>345</v>
       </c>
@@ -16048,7 +16005,7 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>352</v>
       </c>
@@ -16090,7 +16047,7 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>359</v>
       </c>
@@ -16132,7 +16089,7 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>367</v>
       </c>
@@ -16174,7 +16131,7 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
         <v>374</v>
       </c>
@@ -16216,7 +16173,7 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>381</v>
       </c>
@@ -16258,7 +16215,7 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>388</v>
       </c>
@@ -16300,7 +16257,7 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>395</v>
       </c>
@@ -16342,7 +16299,7 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>402</v>
       </c>
@@ -16384,7 +16341,7 @@
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
     </row>
-    <row r="46" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
         <v>410</v>
       </c>
@@ -16426,7 +16383,7 @@
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
     </row>
-    <row r="47" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>417</v>
       </c>
@@ -16468,7 +16425,7 @@
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
     </row>
-    <row r="48" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>424</v>
       </c>
@@ -16510,7 +16467,7 @@
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
     </row>
-    <row r="49" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>431</v>
       </c>
@@ -16552,7 +16509,7 @@
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
     </row>
-    <row r="50" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>438</v>
       </c>
@@ -16594,7 +16551,7 @@
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
     </row>
-    <row r="51" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>445</v>
       </c>
@@ -16636,7 +16593,7 @@
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
     </row>
-    <row r="52" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>452</v>
       </c>
@@ -16678,7 +16635,7 @@
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
     </row>
-    <row r="53" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>459</v>
       </c>
@@ -16720,7 +16677,7 @@
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
     </row>
-    <row r="54" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>466</v>
       </c>
@@ -16762,7 +16719,7 @@
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
     </row>
-    <row r="55" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>473</v>
       </c>
@@ -16804,7 +16761,7 @@
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
     </row>
-    <row r="56" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
         <v>480</v>
       </c>
@@ -16846,7 +16803,7 @@
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
     </row>
-    <row r="57" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>487</v>
       </c>
@@ -16888,7 +16845,7 @@
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
     </row>
-    <row r="58" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>494</v>
       </c>
@@ -16930,7 +16887,7 @@
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
     </row>
-    <row r="59" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>501</v>
       </c>
@@ -16972,7 +16929,7 @@
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
     </row>
-    <row r="60" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
         <v>508</v>
       </c>
@@ -17016,7 +16973,7 @@
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
     </row>
-    <row r="61" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
         <v>518</v>
       </c>
@@ -17060,7 +17017,7 @@
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
     </row>
-    <row r="62" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
         <v>525</v>
       </c>
@@ -17104,7 +17061,7 @@
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
     </row>
-    <row r="63" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>532</v>
       </c>
@@ -17148,7 +17105,7 @@
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
     </row>
-    <row r="64" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>539</v>
       </c>
@@ -17192,7 +17149,7 @@
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
     </row>
-    <row r="65" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>546</v>
       </c>
@@ -17236,7 +17193,7 @@
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
     </row>
-    <row r="66" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>552</v>
       </c>
@@ -17280,7 +17237,7 @@
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
     </row>
-    <row r="67" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>559</v>
       </c>
@@ -17324,7 +17281,7 @@
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
     </row>
-    <row r="68" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>566</v>
       </c>
@@ -17368,7 +17325,7 @@
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
     </row>
-    <row r="69" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>573</v>
       </c>
@@ -17410,7 +17367,7 @@
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
     </row>
-    <row r="70" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>579</v>
       </c>
@@ -17452,7 +17409,7 @@
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
     </row>
-    <row r="71" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>584</v>
       </c>
@@ -17496,7 +17453,7 @@
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
     </row>
-    <row r="72" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>591</v>
       </c>
@@ -17540,7 +17497,7 @@
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
     </row>
-    <row r="73" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
         <v>598</v>
       </c>
@@ -17584,7 +17541,7 @@
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
     </row>
-    <row r="74" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
         <v>604</v>
       </c>
@@ -17628,7 +17585,7 @@
       <c r="Q74" s="2"/>
       <c r="R74" s="2"/>
     </row>
-    <row r="75" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>610</v>
       </c>
@@ -17672,7 +17629,7 @@
       <c r="Q75" s="2"/>
       <c r="R75" s="2"/>
     </row>
-    <row r="76" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
         <v>617</v>
       </c>
@@ -17716,7 +17673,7 @@
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
     </row>
-    <row r="77" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>624</v>
       </c>
@@ -17760,7 +17717,7 @@
       <c r="Q77" s="2"/>
       <c r="R77" s="2"/>
     </row>
-    <row r="78" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
         <v>631</v>
       </c>
@@ -17804,7 +17761,7 @@
       <c r="Q78" s="2"/>
       <c r="R78" s="2"/>
     </row>
-    <row r="79" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>638</v>
       </c>
@@ -17848,7 +17805,7 @@
       <c r="Q79" s="2"/>
       <c r="R79" s="2"/>
     </row>
-    <row r="80" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
         <v>645</v>
       </c>
@@ -17892,7 +17849,7 @@
       <c r="Q80" s="2"/>
       <c r="R80" s="2"/>
     </row>
-    <row r="81" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>652</v>
       </c>
@@ -17936,7 +17893,7 @@
       <c r="Q81" s="2"/>
       <c r="R81" s="2"/>
     </row>
-    <row r="82" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
         <v>659</v>
       </c>
@@ -17980,7 +17937,7 @@
       <c r="Q82" s="2"/>
       <c r="R82" s="2"/>
     </row>
-    <row r="83" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
         <v>666</v>
       </c>
@@ -18026,7 +17983,7 @@
       <c r="Q83" s="2"/>
       <c r="R83" s="2"/>
     </row>
-    <row r="84" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>676</v>
       </c>
@@ -18072,7 +18029,7 @@
       <c r="Q84" s="2"/>
       <c r="R84" s="2"/>
     </row>
-    <row r="85" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>685</v>
       </c>
@@ -18118,7 +18075,7 @@
       <c r="Q85" s="2"/>
       <c r="R85" s="2"/>
     </row>
-    <row r="86" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
         <v>693</v>
       </c>
@@ -18164,7 +18121,7 @@
       <c r="Q86" s="2"/>
       <c r="R86" s="2"/>
     </row>
-    <row r="87" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>701</v>
       </c>
@@ -18210,7 +18167,7 @@
       <c r="Q87" s="2"/>
       <c r="R87" s="2"/>
     </row>
-    <row r="88" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
         <v>710</v>
       </c>
@@ -18256,7 +18213,7 @@
       <c r="Q88" s="2"/>
       <c r="R88" s="2"/>
     </row>
-    <row r="89" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
         <v>719</v>
       </c>
@@ -18302,7 +18259,7 @@
       <c r="Q89" s="2"/>
       <c r="R89" s="2"/>
     </row>
-    <row r="90" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
         <v>727</v>
       </c>
@@ -18346,7 +18303,7 @@
       <c r="Q90" s="2"/>
       <c r="R90" s="2"/>
     </row>
-    <row r="91" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
         <v>734</v>
       </c>
@@ -18392,7 +18349,7 @@
       <c r="Q91" s="2"/>
       <c r="R91" s="2"/>
     </row>
-    <row r="92" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>742</v>
       </c>
@@ -18438,7 +18395,7 @@
       <c r="Q92" s="2"/>
       <c r="R92" s="2"/>
     </row>
-    <row r="93" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
         <v>751</v>
       </c>
@@ -18484,7 +18441,7 @@
       <c r="Q93" s="2"/>
       <c r="R93" s="2"/>
     </row>
-    <row r="94" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
         <v>758</v>
       </c>
@@ -18530,7 +18487,7 @@
       <c r="Q94" s="2"/>
       <c r="R94" s="2"/>
     </row>
-    <row r="95" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
         <v>766</v>
       </c>
@@ -18576,7 +18533,7 @@
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
     </row>
-    <row r="96" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>775</v>
       </c>
@@ -18622,7 +18579,7 @@
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
     </row>
-    <row r="97" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
         <v>783</v>
       </c>
@@ -18668,7 +18625,7 @@
       <c r="Q97" s="2"/>
       <c r="R97" s="2"/>
     </row>
-    <row r="98" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
         <v>792</v>
       </c>
@@ -18714,7 +18671,7 @@
       <c r="Q98" s="2"/>
       <c r="R98" s="2"/>
     </row>
-    <row r="99" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
         <v>801</v>
       </c>
@@ -18760,7 +18717,7 @@
       <c r="Q99" s="2"/>
       <c r="R99" s="2"/>
     </row>
-    <row r="100" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
         <v>808</v>
       </c>
@@ -18806,7 +18763,7 @@
       <c r="Q100" s="2"/>
       <c r="R100" s="2"/>
     </row>
-    <row r="101" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
         <v>816</v>
       </c>
@@ -18852,7 +18809,7 @@
       <c r="Q101" s="2"/>
       <c r="R101" s="2"/>
     </row>
-    <row r="102" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
         <v>824</v>
       </c>
@@ -18898,7 +18855,7 @@
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
     </row>
-    <row r="103" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
         <v>832</v>
       </c>
@@ -18944,7 +18901,7 @@
       <c r="Q103" s="2"/>
       <c r="R103" s="2"/>
     </row>
-    <row r="104" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
         <v>839</v>
       </c>
@@ -18990,7 +18947,7 @@
       <c r="Q104" s="2"/>
       <c r="R104" s="2"/>
     </row>
-    <row r="105" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
         <v>848</v>
       </c>
@@ -19036,7 +18993,7 @@
       <c r="Q105" s="2"/>
       <c r="R105" s="2"/>
     </row>
-    <row r="106" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
         <v>856</v>
       </c>
@@ -19082,7 +19039,7 @@
       <c r="Q106" s="2"/>
       <c r="R106" s="2"/>
     </row>
-    <row r="107" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
         <v>863</v>
       </c>
@@ -19128,7 +19085,7 @@
       <c r="Q107" s="2"/>
       <c r="R107" s="2"/>
     </row>
-    <row r="108" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
         <v>871</v>
       </c>
@@ -19174,7 +19131,7 @@
       <c r="Q108" s="2"/>
       <c r="R108" s="2"/>
     </row>
-    <row r="109" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
         <v>880</v>
       </c>
@@ -19220,7 +19177,7 @@
       <c r="Q109" s="2"/>
       <c r="R109" s="2"/>
     </row>
-    <row r="110" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
         <v>889</v>
       </c>
@@ -19266,7 +19223,7 @@
       <c r="Q110" s="2"/>
       <c r="R110" s="2"/>
     </row>
-    <row r="111" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
         <v>897</v>
       </c>
@@ -19312,7 +19269,7 @@
       <c r="Q111" s="2"/>
       <c r="R111" s="2"/>
     </row>
-    <row r="112" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
         <v>904</v>
       </c>
@@ -19358,7 +19315,7 @@
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
     </row>
-    <row r="113" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
         <v>912</v>
       </c>
@@ -19404,7 +19361,7 @@
       <c r="Q113" s="2"/>
       <c r="R113" s="2"/>
     </row>
-    <row r="114" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
         <v>920</v>
       </c>
@@ -19450,7 +19407,7 @@
       <c r="Q114" s="2"/>
       <c r="R114" s="2"/>
     </row>
-    <row r="115" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
         <v>928</v>
       </c>
@@ -19496,7 +19453,7 @@
       <c r="Q115" s="2"/>
       <c r="R115" s="2"/>
     </row>
-    <row r="116" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
         <v>936</v>
       </c>
@@ -19542,7 +19499,7 @@
       <c r="Q116" s="2"/>
       <c r="R116" s="2"/>
     </row>
-    <row r="117" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
         <v>944</v>
       </c>
@@ -19588,7 +19545,7 @@
       <c r="Q117" s="2"/>
       <c r="R117" s="2"/>
     </row>
-    <row r="118" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
         <v>951</v>
       </c>
@@ -19634,7 +19591,7 @@
       <c r="Q118" s="2"/>
       <c r="R118" s="2"/>
     </row>
-    <row r="119" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="2" t="s">
         <v>959</v>
       </c>
@@ -19680,7 +19637,7 @@
       <c r="Q119" s="2"/>
       <c r="R119" s="2"/>
     </row>
-    <row r="120" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="2" t="s">
         <v>966</v>
       </c>
@@ -19726,7 +19683,7 @@
       <c r="Q120" s="2"/>
       <c r="R120" s="2"/>
     </row>
-    <row r="121" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="2" t="s">
         <v>974</v>
       </c>
@@ -19772,7 +19729,7 @@
       <c r="Q121" s="2"/>
       <c r="R121" s="2"/>
     </row>
-    <row r="122" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
         <v>982</v>
       </c>
@@ -19818,7 +19775,7 @@
       <c r="Q122" s="2"/>
       <c r="R122" s="2"/>
     </row>
-    <row r="123" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="2" t="s">
         <v>990</v>
       </c>
@@ -19864,7 +19821,7 @@
       <c r="Q123" s="2"/>
       <c r="R123" s="2"/>
     </row>
-    <row r="124" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
         <v>999</v>
       </c>
@@ -19910,7 +19867,7 @@
       <c r="Q124" s="2"/>
       <c r="R124" s="2"/>
     </row>
-    <row r="125" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="2" t="s">
         <v>1007</v>
       </c>
@@ -19956,7 +19913,7 @@
       <c r="Q125" s="2"/>
       <c r="R125" s="2"/>
     </row>
-    <row r="126" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="2" t="s">
         <v>1014</v>
       </c>
@@ -20002,7 +19959,7 @@
       <c r="Q126" s="2"/>
       <c r="R126" s="2"/>
     </row>
-    <row r="127" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
         <v>1022</v>
       </c>
@@ -20048,7 +20005,7 @@
       <c r="Q127" s="2"/>
       <c r="R127" s="2"/>
     </row>
-    <row r="128" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
         <v>1030</v>
       </c>
@@ -20094,7 +20051,7 @@
       <c r="Q128" s="2"/>
       <c r="R128" s="2"/>
     </row>
-    <row r="129" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
         <v>1038</v>
       </c>
@@ -20140,7 +20097,7 @@
       <c r="Q129" s="2"/>
       <c r="R129" s="2"/>
     </row>
-    <row r="130" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="2" t="s">
         <v>1046</v>
       </c>
@@ -20186,7 +20143,7 @@
       <c r="Q130" s="2"/>
       <c r="R130" s="2"/>
     </row>
-    <row r="131" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="2" t="s">
         <v>1054</v>
       </c>
@@ -20232,7 +20189,7 @@
       <c r="Q131" s="2"/>
       <c r="R131" s="2"/>
     </row>
-    <row r="132" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="2" t="s">
         <v>1062</v>
       </c>
@@ -20278,7 +20235,7 @@
       <c r="Q132" s="2"/>
       <c r="R132" s="2"/>
     </row>
-    <row r="133" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A133" s="2" t="s">
         <v>1072</v>
       </c>
@@ -20324,7 +20281,7 @@
       <c r="Q133" s="2"/>
       <c r="R133" s="2"/>
     </row>
-    <row r="134" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="2" t="s">
         <v>1080</v>
       </c>
@@ -20370,7 +20327,7 @@
       <c r="Q134" s="2"/>
       <c r="R134" s="2"/>
     </row>
-    <row r="135" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="2" t="s">
         <v>1087</v>
       </c>
@@ -20416,7 +20373,7 @@
       <c r="Q135" s="2"/>
       <c r="R135" s="2"/>
     </row>
-    <row r="136" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A136" s="2" t="s">
         <v>1095</v>
       </c>
@@ -20462,7 +20419,7 @@
       <c r="Q136" s="2"/>
       <c r="R136" s="2"/>
     </row>
-    <row r="137" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
         <v>1103</v>
       </c>
@@ -20506,7 +20463,7 @@
       <c r="Q137" s="2"/>
       <c r="R137" s="2"/>
     </row>
-    <row r="138" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
         <v>1111</v>
       </c>
@@ -20550,7 +20507,7 @@
       <c r="Q138" s="2"/>
       <c r="R138" s="2"/>
     </row>
-    <row r="139" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="2" t="s">
         <v>1118</v>
       </c>
@@ -20596,7 +20553,7 @@
       <c r="Q139" s="2"/>
       <c r="R139" s="2"/>
     </row>
-    <row r="140" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
         <v>1126</v>
       </c>
@@ -20642,7 +20599,7 @@
       <c r="Q140" s="2"/>
       <c r="R140" s="2"/>
     </row>
-    <row r="141" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
         <v>1134</v>
       </c>
@@ -20688,7 +20645,7 @@
       <c r="Q141" s="2"/>
       <c r="R141" s="2"/>
     </row>
-    <row r="142" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A142" s="2" t="s">
         <v>1141</v>
       </c>
@@ -20734,7 +20691,7 @@
       <c r="Q142" s="2"/>
       <c r="R142" s="2"/>
     </row>
-    <row r="143" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="2" t="s">
         <v>1150</v>
       </c>
@@ -20780,7 +20737,7 @@
       <c r="Q143" s="2"/>
       <c r="R143" s="2"/>
     </row>
-    <row r="144" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A144" s="2" t="s">
         <v>1158</v>
       </c>
@@ -20826,7 +20783,7 @@
       <c r="Q144" s="2"/>
       <c r="R144" s="2"/>
     </row>
-    <row r="145" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A145" s="2" t="s">
         <v>1166</v>
       </c>
@@ -20870,7 +20827,7 @@
       <c r="Q145" s="2"/>
       <c r="R145" s="2"/>
     </row>
-    <row r="146" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A146" s="2" t="s">
         <v>1174</v>
       </c>
@@ -20916,7 +20873,7 @@
       <c r="Q146" s="2"/>
       <c r="R146" s="2"/>
     </row>
-    <row r="147" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
         <v>1182</v>
       </c>
@@ -20962,7 +20919,7 @@
       <c r="Q147" s="2"/>
       <c r="R147" s="2"/>
     </row>
-    <row r="148" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
         <v>1190</v>
       </c>
@@ -21008,7 +20965,7 @@
       <c r="Q148" s="2"/>
       <c r="R148" s="2"/>
     </row>
-    <row r="149" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
         <v>1197</v>
       </c>
@@ -21054,7 +21011,7 @@
       <c r="Q149" s="2"/>
       <c r="R149" s="2"/>
     </row>
-    <row r="150" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
         <v>1205</v>
       </c>
@@ -21100,7 +21057,7 @@
       <c r="Q150" s="2"/>
       <c r="R150" s="2"/>
     </row>
-    <row r="151" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
         <v>1212</v>
       </c>
@@ -21146,7 +21103,7 @@
       <c r="Q151" s="2"/>
       <c r="R151" s="2"/>
     </row>
-    <row r="152" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
         <v>1219</v>
       </c>
@@ -21192,7 +21149,7 @@
       <c r="Q152" s="2"/>
       <c r="R152" s="2"/>
     </row>
-    <row r="153" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="2" t="s">
         <v>1228</v>
       </c>
@@ -21238,7 +21195,7 @@
       <c r="Q153" s="2"/>
       <c r="R153" s="2"/>
     </row>
-    <row r="154" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A154" s="2" t="s">
         <v>1235</v>
       </c>
@@ -21284,7 +21241,7 @@
       <c r="Q154" s="2"/>
       <c r="R154" s="2"/>
     </row>
-    <row r="155" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A155" s="2" t="s">
         <v>1243</v>
       </c>
@@ -21330,7 +21287,7 @@
       <c r="Q155" s="2"/>
       <c r="R155" s="2"/>
     </row>
-    <row r="156" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A156" s="2" t="s">
         <v>1251</v>
       </c>
@@ -21376,7 +21333,7 @@
       <c r="Q156" s="2"/>
       <c r="R156" s="2"/>
     </row>
-    <row r="157" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A157" s="2" t="s">
         <v>1258</v>
       </c>
@@ -21422,7 +21379,7 @@
       <c r="Q157" s="2"/>
       <c r="R157" s="2"/>
     </row>
-    <row r="158" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A158" s="2" t="s">
         <v>1266</v>
       </c>
@@ -21468,7 +21425,7 @@
       <c r="Q158" s="2"/>
       <c r="R158" s="2"/>
     </row>
-    <row r="159" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A159" s="2" t="s">
         <v>1274</v>
       </c>
@@ -21514,7 +21471,7 @@
       <c r="Q159" s="2"/>
       <c r="R159" s="2"/>
     </row>
-    <row r="160" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A160" s="2" t="s">
         <v>1281</v>
       </c>
@@ -21558,7 +21515,7 @@
       <c r="Q160" s="2"/>
       <c r="R160" s="2"/>
     </row>
-    <row r="161" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A161" s="2" t="s">
         <v>1288</v>
       </c>
@@ -21604,7 +21561,7 @@
       <c r="Q161" s="2"/>
       <c r="R161" s="2"/>
     </row>
-    <row r="162" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A162" s="2" t="s">
         <v>1296</v>
       </c>
@@ -21650,7 +21607,7 @@
       <c r="Q162" s="2"/>
       <c r="R162" s="2"/>
     </row>
-    <row r="163" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A163" s="2" t="s">
         <v>1304</v>
       </c>
@@ -21696,7 +21653,7 @@
       <c r="Q163" s="2"/>
       <c r="R163" s="2"/>
     </row>
-    <row r="164" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A164" s="2" t="s">
         <v>1313</v>
       </c>
@@ -21742,7 +21699,7 @@
       <c r="Q164" s="2"/>
       <c r="R164" s="2"/>
     </row>
-    <row r="165" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A165" s="2" t="s">
         <v>1321</v>
       </c>
@@ -21788,7 +21745,7 @@
       <c r="Q165" s="2"/>
       <c r="R165" s="2"/>
     </row>
-    <row r="166" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A166" s="2" t="s">
         <v>1329</v>
       </c>
@@ -21832,7 +21789,7 @@
       <c r="Q166" s="2"/>
       <c r="R166" s="2"/>
     </row>
-    <row r="167" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A167" s="2" t="s">
         <v>1335</v>
       </c>
@@ -21878,7 +21835,7 @@
       <c r="Q167" s="2"/>
       <c r="R167" s="2"/>
     </row>
-    <row r="168" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A168" s="2" t="s">
         <v>1342</v>
       </c>
@@ -21924,7 +21881,7 @@
       <c r="Q168" s="2"/>
       <c r="R168" s="2"/>
     </row>
-    <row r="169" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A169" s="2" t="s">
         <v>1349</v>
       </c>
@@ -21970,7 +21927,7 @@
       <c r="Q169" s="2"/>
       <c r="R169" s="2"/>
     </row>
-    <row r="170" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A170" s="2" t="s">
         <v>1356</v>
       </c>
@@ -22016,7 +21973,7 @@
       <c r="Q170" s="2"/>
       <c r="R170" s="2"/>
     </row>
-    <row r="171" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="2" t="s">
         <v>1364</v>
       </c>
@@ -22060,7 +22017,7 @@
       <c r="Q171" s="2"/>
       <c r="R171" s="2"/>
     </row>
-    <row r="172" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="2" t="s">
         <v>1371</v>
       </c>
@@ -22106,7 +22063,7 @@
       <c r="Q172" s="2"/>
       <c r="R172" s="2"/>
     </row>
-    <row r="173" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="2" t="s">
         <v>1379</v>
       </c>
@@ -22152,7 +22109,7 @@
       <c r="Q173" s="2"/>
       <c r="R173" s="2"/>
     </row>
-    <row r="174" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="2" t="s">
         <v>1387</v>
       </c>
@@ -22198,7 +22155,7 @@
       <c r="Q174" s="2"/>
       <c r="R174" s="2"/>
     </row>
-    <row r="175" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="2" t="s">
         <v>1395</v>
       </c>
@@ -22242,7 +22199,7 @@
       <c r="Q175" s="2"/>
       <c r="R175" s="2"/>
     </row>
-    <row r="176" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="2" t="s">
         <v>1401</v>
       </c>
@@ -22286,7 +22243,7 @@
       <c r="Q176" s="2"/>
       <c r="R176" s="2"/>
     </row>
-    <row r="177" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="2" t="s">
         <v>1409</v>
       </c>
@@ -22330,7 +22287,7 @@
       <c r="Q177" s="2"/>
       <c r="R177" s="2"/>
     </row>
-    <row r="178" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="2" t="s">
         <v>1415</v>
       </c>
@@ -22376,7 +22333,7 @@
       <c r="Q178" s="2"/>
       <c r="R178" s="2"/>
     </row>
-    <row r="179" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="2" t="s">
         <v>1423</v>
       </c>
@@ -22422,7 +22379,7 @@
       <c r="Q179" s="2"/>
       <c r="R179" s="2"/>
     </row>
-    <row r="180" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="2" t="s">
         <v>1431</v>
       </c>
@@ -22468,7 +22425,7 @@
       <c r="Q180" s="2"/>
       <c r="R180" s="2"/>
     </row>
-    <row r="181" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="2" t="s">
         <v>1439</v>
       </c>
@@ -22514,7 +22471,7 @@
       <c r="Q181" s="2"/>
       <c r="R181" s="2"/>
     </row>
-    <row r="182" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="2" t="s">
         <v>1448</v>
       </c>
@@ -22558,7 +22515,7 @@
       <c r="Q182" s="2"/>
       <c r="R182" s="2"/>
     </row>
-    <row r="183" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="2" t="s">
         <v>1455</v>
       </c>
@@ -22604,7 +22561,7 @@
       <c r="Q183" s="2"/>
       <c r="R183" s="2"/>
     </row>
-    <row r="184" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="2" t="s">
         <v>1462</v>
       </c>
@@ -22650,7 +22607,7 @@
       <c r="Q184" s="2"/>
       <c r="R184" s="2"/>
     </row>
-    <row r="185" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="2" t="s">
         <v>1470</v>
       </c>
@@ -22696,7 +22653,7 @@
       <c r="Q185" s="2"/>
       <c r="R185" s="2"/>
     </row>
-    <row r="186" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="2" t="s">
         <v>1479</v>
       </c>
@@ -22742,7 +22699,7 @@
       <c r="Q186" s="2"/>
       <c r="R186" s="2"/>
     </row>
-    <row r="187" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A187" s="2" t="s">
         <v>1487</v>
       </c>
@@ -22788,7 +22745,7 @@
       <c r="Q187" s="2"/>
       <c r="R187" s="2"/>
     </row>
-    <row r="188" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A188" s="2" t="s">
         <v>1495</v>
       </c>
@@ -22834,7 +22791,7 @@
       <c r="Q188" s="2"/>
       <c r="R188" s="2"/>
     </row>
-    <row r="189" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A189" s="2" t="s">
         <v>1502</v>
       </c>
@@ -22880,7 +22837,7 @@
       <c r="Q189" s="2"/>
       <c r="R189" s="2"/>
     </row>
-    <row r="190" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A190" s="2" t="s">
         <v>1511</v>
       </c>
@@ -22932,15 +22889,15 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="N5:N190">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$N5="Exclude"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$N5="Include"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O190">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND($N5="Exclude",$O5="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22976,15 +22933,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M189"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="70.7109375" customWidth="1"/>
-    <col min="3" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="13" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" customWidth="1"/>
+    <col min="2" max="2" width="70.73046875" customWidth="1"/>
+    <col min="3" max="4" width="14.73046875" customWidth="1"/>
+    <col min="5" max="13" width="24.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>1519</v>
       </c>
@@ -23001,7 +22958,7 @@
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
@@ -23042,7 +22999,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>68</v>
       </c>
@@ -23083,7 +23040,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>81</v>
       </c>
@@ -23118,7 +23075,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>93</v>
       </c>
@@ -23153,7 +23110,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>104</v>
       </c>
@@ -23188,7 +23145,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>114</v>
       </c>
@@ -23223,7 +23180,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>123</v>
       </c>
@@ -23258,7 +23215,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>132</v>
       </c>
@@ -23293,7 +23250,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>139</v>
       </c>
@@ -23328,7 +23285,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>148</v>
       </c>
@@ -23363,7 +23320,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>157</v>
       </c>
@@ -23398,7 +23355,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>166</v>
       </c>
@@ -23433,7 +23390,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>175</v>
       </c>
@@ -23468,7 +23425,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>185</v>
       </c>
@@ -23503,7 +23460,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>194</v>
       </c>
@@ -23538,7 +23495,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>204</v>
       </c>
@@ -23573,7 +23530,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>212</v>
       </c>
@@ -23608,7 +23565,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>220</v>
       </c>
@@ -23643,7 +23600,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>228</v>
       </c>
@@ -23678,7 +23635,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
@@ -23713,7 +23670,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>245</v>
       </c>
@@ -23748,7 +23705,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>254</v>
       </c>
@@ -23783,7 +23740,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>261</v>
       </c>
@@ -23818,7 +23775,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>268</v>
       </c>
@@ -23853,7 +23810,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>277</v>
       </c>
@@ -23888,7 +23845,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>285</v>
       </c>
@@ -23923,7 +23880,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>292</v>
       </c>
@@ -23958,7 +23915,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>300</v>
       </c>
@@ -23993,7 +23950,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>309</v>
       </c>
@@ -24028,7 +23985,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>317</v>
       </c>
@@ -24063,7 +24020,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>324</v>
       </c>
@@ -24098,7 +24055,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>331</v>
       </c>
@@ -24133,7 +24090,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>338</v>
       </c>
@@ -24168,7 +24125,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>345</v>
       </c>
@@ -24203,7 +24160,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>352</v>
       </c>
@@ -24238,7 +24195,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>359</v>
       </c>
@@ -24273,7 +24230,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>367</v>
       </c>
@@ -24308,7 +24265,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>374</v>
       </c>
@@ -24343,7 +24300,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
         <v>381</v>
       </c>
@@ -24378,7 +24335,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>388</v>
       </c>
@@ -24413,7 +24370,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>395</v>
       </c>
@@ -24448,7 +24405,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>402</v>
       </c>
@@ -24483,7 +24440,7 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>410</v>
       </c>
@@ -24518,7 +24475,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
         <v>417</v>
       </c>
@@ -24553,7 +24510,7 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
     </row>
-    <row r="47" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>424</v>
       </c>
@@ -24588,7 +24545,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>431</v>
       </c>
@@ -24623,7 +24580,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>438</v>
       </c>
@@ -24658,7 +24615,7 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>445</v>
       </c>
@@ -24693,7 +24650,7 @@
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>452</v>
       </c>
@@ -24728,7 +24685,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>459</v>
       </c>
@@ -24763,7 +24720,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>466</v>
       </c>
@@ -24798,7 +24755,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>473</v>
       </c>
@@ -24833,7 +24790,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>480</v>
       </c>
@@ -24868,7 +24825,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
         <v>487</v>
       </c>
@@ -24903,7 +24860,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>494</v>
       </c>
@@ -24938,7 +24895,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>501</v>
       </c>
@@ -24973,7 +24930,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>508</v>
       </c>
@@ -25008,7 +24965,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
         <v>518</v>
       </c>
@@ -25043,7 +25000,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
         <v>525</v>
       </c>
@@ -25078,7 +25035,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
         <v>532</v>
       </c>
@@ -25113,7 +25070,7 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>539</v>
       </c>
@@ -25148,7 +25105,7 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>546</v>
       </c>
@@ -25183,7 +25140,7 @@
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
     </row>
-    <row r="65" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>552</v>
       </c>
@@ -25218,7 +25175,7 @@
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>559</v>
       </c>
@@ -25253,7 +25210,7 @@
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
     </row>
-    <row r="67" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>566</v>
       </c>
@@ -25288,7 +25245,7 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
     </row>
-    <row r="68" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>573</v>
       </c>
@@ -25323,7 +25280,7 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
     </row>
-    <row r="69" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>579</v>
       </c>
@@ -25358,7 +25315,7 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
     </row>
-    <row r="70" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>584</v>
       </c>
@@ -25393,7 +25350,7 @@
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
     </row>
-    <row r="71" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>591</v>
       </c>
@@ -25428,7 +25385,7 @@
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
     </row>
-    <row r="72" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>598</v>
       </c>
@@ -25463,7 +25420,7 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
     </row>
-    <row r="73" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
         <v>604</v>
       </c>
@@ -25498,7 +25455,7 @@
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
     </row>
-    <row r="74" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
         <v>610</v>
       </c>
@@ -25533,7 +25490,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
     </row>
-    <row r="75" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>617</v>
       </c>
@@ -25568,7 +25525,7 @@
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
     </row>
-    <row r="76" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
         <v>624</v>
       </c>
@@ -25603,7 +25560,7 @@
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
     </row>
-    <row r="77" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>631</v>
       </c>
@@ -25638,7 +25595,7 @@
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
     </row>
-    <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
         <v>638</v>
       </c>
@@ -25673,7 +25630,7 @@
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
     </row>
-    <row r="79" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>645</v>
       </c>
@@ -25708,7 +25665,7 @@
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
     </row>
-    <row r="80" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
         <v>652</v>
       </c>
@@ -25743,7 +25700,7 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
     </row>
-    <row r="81" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>659</v>
       </c>
@@ -25778,7 +25735,7 @@
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
     </row>
-    <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
         <v>666</v>
       </c>
@@ -25813,7 +25770,7 @@
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
         <v>676</v>
       </c>
@@ -25848,7 +25805,7 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
     </row>
-    <row r="84" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>685</v>
       </c>
@@ -25883,7 +25840,7 @@
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>693</v>
       </c>
@@ -25918,7 +25875,7 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
         <v>701</v>
       </c>
@@ -25953,7 +25910,7 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>710</v>
       </c>
@@ -25988,7 +25945,7 @@
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
     </row>
-    <row r="88" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
         <v>719</v>
       </c>
@@ -26023,7 +25980,7 @@
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
         <v>727</v>
       </c>
@@ -26058,7 +26015,7 @@
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
     </row>
-    <row r="90" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
         <v>734</v>
       </c>
@@ -26093,7 +26050,7 @@
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
     </row>
-    <row r="91" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
         <v>742</v>
       </c>
@@ -26128,7 +26085,7 @@
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
     </row>
-    <row r="92" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>751</v>
       </c>
@@ -26163,7 +26120,7 @@
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
     </row>
-    <row r="93" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
         <v>758</v>
       </c>
@@ -26198,7 +26155,7 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
     </row>
-    <row r="94" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
         <v>766</v>
       </c>
@@ -26233,7 +26190,7 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
     </row>
-    <row r="95" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
         <v>775</v>
       </c>
@@ -26268,7 +26225,7 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
     </row>
-    <row r="96" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>783</v>
       </c>
@@ -26303,7 +26260,7 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
     </row>
-    <row r="97" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
         <v>792</v>
       </c>
@@ -26338,7 +26295,7 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
     </row>
-    <row r="98" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
         <v>801</v>
       </c>
@@ -26373,7 +26330,7 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
     </row>
-    <row r="99" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
         <v>808</v>
       </c>
@@ -26408,7 +26365,7 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
     </row>
-    <row r="100" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
         <v>816</v>
       </c>
@@ -26443,7 +26400,7 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
     </row>
-    <row r="101" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
         <v>824</v>
       </c>
@@ -26478,7 +26435,7 @@
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
     </row>
-    <row r="102" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
         <v>832</v>
       </c>
@@ -26513,7 +26470,7 @@
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
     </row>
-    <row r="103" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
         <v>839</v>
       </c>
@@ -26548,7 +26505,7 @@
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
     </row>
-    <row r="104" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
         <v>848</v>
       </c>
@@ -26583,7 +26540,7 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
     </row>
-    <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
         <v>856</v>
       </c>
@@ -26618,7 +26575,7 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
     </row>
-    <row r="106" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
         <v>863</v>
       </c>
@@ -26653,7 +26610,7 @@
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
     </row>
-    <row r="107" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
         <v>871</v>
       </c>
@@ -26688,7 +26645,7 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
     </row>
-    <row r="108" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
         <v>880</v>
       </c>
@@ -26723,7 +26680,7 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
     </row>
-    <row r="109" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
         <v>889</v>
       </c>
@@ -26758,7 +26715,7 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
     </row>
-    <row r="110" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
         <v>897</v>
       </c>
@@ -26793,7 +26750,7 @@
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
     </row>
-    <row r="111" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
         <v>904</v>
       </c>
@@ -26828,7 +26785,7 @@
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
     </row>
-    <row r="112" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
         <v>912</v>
       </c>
@@ -26863,7 +26820,7 @@
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
     </row>
-    <row r="113" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
         <v>920</v>
       </c>
@@ -26898,7 +26855,7 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
     </row>
-    <row r="114" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
         <v>928</v>
       </c>
@@ -26933,7 +26890,7 @@
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
     </row>
-    <row r="115" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
         <v>936</v>
       </c>
@@ -26968,7 +26925,7 @@
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
     </row>
-    <row r="116" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -27003,7 +26960,7 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
     </row>
-    <row r="117" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
         <v>951</v>
       </c>
@@ -27038,7 +26995,7 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
     </row>
-    <row r="118" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
         <v>959</v>
       </c>
@@ -27073,7 +27030,7 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
     </row>
-    <row r="119" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A119" s="2" t="s">
         <v>966</v>
       </c>
@@ -27108,7 +27065,7 @@
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
     </row>
-    <row r="120" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A120" s="2" t="s">
         <v>974</v>
       </c>
@@ -27143,7 +27100,7 @@
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
     </row>
-    <row r="121" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A121" s="2" t="s">
         <v>982</v>
       </c>
@@ -27178,7 +27135,7 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
     </row>
-    <row r="122" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
         <v>990</v>
       </c>
@@ -27213,7 +27170,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
     </row>
-    <row r="123" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A123" s="2" t="s">
         <v>999</v>
       </c>
@@ -27248,7 +27205,7 @@
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
     </row>
-    <row r="124" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
         <v>1007</v>
       </c>
@@ -27283,7 +27240,7 @@
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
     </row>
-    <row r="125" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A125" s="2" t="s">
         <v>1014</v>
       </c>
@@ -27318,7 +27275,7 @@
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
     </row>
-    <row r="126" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A126" s="2" t="s">
         <v>1022</v>
       </c>
@@ -27353,7 +27310,7 @@
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
     </row>
-    <row r="127" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
         <v>1030</v>
       </c>
@@ -27388,7 +27345,7 @@
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
     </row>
-    <row r="128" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
         <v>1038</v>
       </c>
@@ -27423,7 +27380,7 @@
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
     </row>
-    <row r="129" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
         <v>1046</v>
       </c>
@@ -27458,7 +27415,7 @@
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
     </row>
-    <row r="130" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A130" s="2" t="s">
         <v>1054</v>
       </c>
@@ -27493,7 +27450,7 @@
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
     </row>
-    <row r="131" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A131" s="2" t="s">
         <v>1062</v>
       </c>
@@ -27528,7 +27485,7 @@
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
     </row>
-    <row r="132" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A132" s="2" t="s">
         <v>1072</v>
       </c>
@@ -27563,7 +27520,7 @@
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
     </row>
-    <row r="133" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A133" s="2" t="s">
         <v>1080</v>
       </c>
@@ -27598,7 +27555,7 @@
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
     </row>
-    <row r="134" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A134" s="2" t="s">
         <v>1087</v>
       </c>
@@ -27633,7 +27590,7 @@
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
     </row>
-    <row r="135" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A135" s="2" t="s">
         <v>1095</v>
       </c>
@@ -27668,7 +27625,7 @@
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A136" s="2" t="s">
         <v>1103</v>
       </c>
@@ -27703,7 +27660,7 @@
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
     </row>
-    <row r="137" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
         <v>1111</v>
       </c>
@@ -27738,7 +27695,7 @@
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
     </row>
-    <row r="138" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
         <v>1118</v>
       </c>
@@ -27773,7 +27730,7 @@
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
     </row>
-    <row r="139" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A139" s="2" t="s">
         <v>1126</v>
       </c>
@@ -27808,7 +27765,7 @@
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
     </row>
-    <row r="140" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
         <v>1134</v>
       </c>
@@ -27843,7 +27800,7 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
     </row>
-    <row r="141" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
         <v>1141</v>
       </c>
@@ -27878,7 +27835,7 @@
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
     </row>
-    <row r="142" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A142" s="2" t="s">
         <v>1150</v>
       </c>
@@ -27913,7 +27870,7 @@
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
     </row>
-    <row r="143" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A143" s="2" t="s">
         <v>1158</v>
       </c>
@@ -27948,7 +27905,7 @@
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
     </row>
-    <row r="144" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A144" s="2" t="s">
         <v>1166</v>
       </c>
@@ -27983,7 +27940,7 @@
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
     </row>
-    <row r="145" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A145" s="2" t="s">
         <v>1174</v>
       </c>
@@ -28018,7 +27975,7 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
     </row>
-    <row r="146" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A146" s="2" t="s">
         <v>1182</v>
       </c>
@@ -28053,7 +28010,7 @@
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
     </row>
-    <row r="147" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
         <v>1190</v>
       </c>
@@ -28088,7 +28045,7 @@
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
     </row>
-    <row r="148" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
         <v>1197</v>
       </c>
@@ -28123,7 +28080,7 @@
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
     </row>
-    <row r="149" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
         <v>1205</v>
       </c>
@@ -28158,7 +28115,7 @@
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
     </row>
-    <row r="150" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
         <v>1212</v>
       </c>
@@ -28193,7 +28150,7 @@
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
     </row>
-    <row r="151" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
         <v>1219</v>
       </c>
@@ -28228,7 +28185,7 @@
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
     </row>
-    <row r="152" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
         <v>1228</v>
       </c>
@@ -28263,7 +28220,7 @@
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
     </row>
-    <row r="153" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A153" s="2" t="s">
         <v>1235</v>
       </c>
@@ -28298,7 +28255,7 @@
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
     </row>
-    <row r="154" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A154" s="2" t="s">
         <v>1243</v>
       </c>
@@ -28333,7 +28290,7 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
     </row>
-    <row r="155" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A155" s="2" t="s">
         <v>1251</v>
       </c>
@@ -28368,7 +28325,7 @@
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
     </row>
-    <row r="156" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A156" s="2" t="s">
         <v>1258</v>
       </c>
@@ -28403,7 +28360,7 @@
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
     </row>
-    <row r="157" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A157" s="2" t="s">
         <v>1266</v>
       </c>
@@ -28438,7 +28395,7 @@
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
     </row>
-    <row r="158" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A158" s="2" t="s">
         <v>1274</v>
       </c>
@@ -28473,7 +28430,7 @@
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
     </row>
-    <row r="159" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A159" s="2" t="s">
         <v>1281</v>
       </c>
@@ -28508,7 +28465,7 @@
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
     </row>
-    <row r="160" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A160" s="2" t="s">
         <v>1288</v>
       </c>
@@ -28543,7 +28500,7 @@
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
     </row>
-    <row r="161" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A161" s="2" t="s">
         <v>1296</v>
       </c>
@@ -28578,7 +28535,7 @@
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
     </row>
-    <row r="162" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A162" s="2" t="s">
         <v>1304</v>
       </c>
@@ -28613,7 +28570,7 @@
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
     </row>
-    <row r="163" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A163" s="2" t="s">
         <v>1313</v>
       </c>
@@ -28648,7 +28605,7 @@
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
     </row>
-    <row r="164" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A164" s="2" t="s">
         <v>1321</v>
       </c>
@@ -28683,7 +28640,7 @@
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
     </row>
-    <row r="165" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A165" s="2" t="s">
         <v>1329</v>
       </c>
@@ -28718,7 +28675,7 @@
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
     </row>
-    <row r="166" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A166" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28753,7 +28710,7 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
     </row>
-    <row r="167" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A167" s="2" t="s">
         <v>1342</v>
       </c>
@@ -28788,7 +28745,7 @@
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
     </row>
-    <row r="168" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A168" s="2" t="s">
         <v>1349</v>
       </c>
@@ -28823,7 +28780,7 @@
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
     </row>
-    <row r="169" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A169" s="2" t="s">
         <v>1356</v>
       </c>
@@ -28858,7 +28815,7 @@
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
     </row>
-    <row r="170" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A170" s="2" t="s">
         <v>1364</v>
       </c>
@@ -28893,7 +28850,7 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
     </row>
-    <row r="171" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A171" s="2" t="s">
         <v>1371</v>
       </c>
@@ -28928,7 +28885,7 @@
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
     </row>
-    <row r="172" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" ht="114" x14ac:dyDescent="0.45">
       <c r="A172" s="2" t="s">
         <v>1379</v>
       </c>
@@ -28963,7 +28920,7 @@
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
     </row>
-    <row r="173" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A173" s="2" t="s">
         <v>1387</v>
       </c>
@@ -28998,7 +28955,7 @@
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
     </row>
-    <row r="174" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A174" s="2" t="s">
         <v>1395</v>
       </c>
@@ -29033,7 +28990,7 @@
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
     </row>
-    <row r="175" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A175" s="2" t="s">
         <v>1401</v>
       </c>
@@ -29068,7 +29025,7 @@
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
     </row>
-    <row r="176" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" ht="114" x14ac:dyDescent="0.45">
       <c r="A176" s="2" t="s">
         <v>1409</v>
       </c>
@@ -29103,7 +29060,7 @@
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
     </row>
-    <row r="177" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A177" s="2" t="s">
         <v>1415</v>
       </c>
@@ -29138,7 +29095,7 @@
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
     </row>
-    <row r="178" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A178" s="2" t="s">
         <v>1423</v>
       </c>
@@ -29173,7 +29130,7 @@
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
     </row>
-    <row r="179" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A179" s="2" t="s">
         <v>1431</v>
       </c>
@@ -29208,7 +29165,7 @@
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
     </row>
-    <row r="180" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A180" s="2" t="s">
         <v>1439</v>
       </c>
@@ -29243,7 +29200,7 @@
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
     </row>
-    <row r="181" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A181" s="2" t="s">
         <v>1448</v>
       </c>
@@ -29278,7 +29235,7 @@
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
     </row>
-    <row r="182" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A182" s="2" t="s">
         <v>1455</v>
       </c>
@@ -29313,7 +29270,7 @@
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
     </row>
-    <row r="183" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A183" s="2" t="s">
         <v>1462</v>
       </c>
@@ -29348,7 +29305,7 @@
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
     </row>
-    <row r="184" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A184" s="2" t="s">
         <v>1470</v>
       </c>
@@ -29383,7 +29340,7 @@
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
     </row>
-    <row r="185" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A185" s="2" t="s">
         <v>1479</v>
       </c>
@@ -29418,7 +29375,7 @@
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
     </row>
-    <row r="186" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A186" s="2" t="s">
         <v>1487</v>
       </c>
@@ -29453,7 +29410,7 @@
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
     </row>
-    <row r="187" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A187" s="2" t="s">
         <v>1495</v>
       </c>
@@ -29488,7 +29445,7 @@
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
     </row>
-    <row r="188" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A188" s="2" t="s">
         <v>1502</v>
       </c>
@@ -29523,7 +29480,7 @@
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
     </row>
-    <row r="189" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" ht="114" x14ac:dyDescent="0.45">
       <c r="A189" s="2" t="s">
         <v>1511</v>
       </c>
@@ -29565,7 +29522,7 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="H4:H189">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$H4="Conflict"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29595,19 +29552,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.73046875" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>1529</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>52</v>
       </c>
@@ -29615,7 +29572,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>667</v>
       </c>
@@ -29623,7 +29580,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>278</v>
       </c>
@@ -29631,7 +29588,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>509</v>
       </c>
@@ -29639,7 +29596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>82</v>
       </c>
@@ -29647,7 +29604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>69</v>
       </c>
@@ -29655,7 +29612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>1531</v>
       </c>
@@ -29676,9 +29633,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -29692,7 +29649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -29706,7 +29663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -29720,7 +29677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -29734,42 +29691,42 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>21</v>
       </c>
